--- a/artfynd/A 9807-2026 artfynd.xlsx
+++ b/artfynd/A 9807-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130149436</v>
+        <v>130149705</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,11 +703,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675058</v>
+        <v>674976</v>
       </c>
       <c r="R2" t="n">
-        <v>6605650</v>
+        <v>6605605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130149985</v>
+        <v>130149374</v>
       </c>
       <c r="B3" t="n">
-        <v>58224</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,7 +809,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674964</v>
+        <v>675048</v>
       </c>
       <c r="R3" t="n">
-        <v>6605634</v>
+        <v>6605702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130149439</v>
+        <v>130149434</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674983</v>
+        <v>675105</v>
       </c>
       <c r="R4" t="n">
-        <v>6605658</v>
+        <v>6605641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130149376</v>
+        <v>130149436</v>
       </c>
       <c r="B5" t="n">
-        <v>58532</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675045</v>
+        <v>675058</v>
       </c>
       <c r="R5" t="n">
-        <v>6605653</v>
+        <v>6605650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130149705</v>
+        <v>130149439</v>
       </c>
       <c r="B6" t="n">
-        <v>58393</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1139,7 +1139,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1151,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>674976</v>
+        <v>674983</v>
       </c>
       <c r="R6" t="n">
-        <v>6605605</v>
+        <v>6605658</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,12 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1224,7 @@
         <v>130149703</v>
       </c>
       <c r="B7" t="n">
-        <v>58224</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130149434</v>
+        <v>130149985</v>
       </c>
       <c r="B8" t="n">
-        <v>58224</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,11 +1355,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675105</v>
+        <v>674964</v>
       </c>
       <c r="R8" t="n">
-        <v>6605641</v>
+        <v>6605634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,6 +1426,116 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Artinventeringar Molnby-Ubby</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130149376</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Molnby-Ubby, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>675045</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6605653</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Artinventeringar Molnby-Ubby</t>
         </is>
